--- a/_903_MissionsText.xlsx
+++ b/_903_MissionsText.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF615CF1-A83B-4820-8201-B1E9541C28E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0FAD44-84CF-41D0-9D92-564396928023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="11332" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -144,12 +144,65 @@
     <t>業務を{0}回完了する。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>ログインする。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Log in {0} times.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>{0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>回ログインする</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Gulim"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그인 {0}회 하기.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그인 하기.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Log In.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,6 +258,13 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -246,7 +306,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -260,6 +320,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -637,13 +700,13 @@
         <v>9030001</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="3" customFormat="1" ht="17.649999999999999">
@@ -651,13 +714,13 @@
         <v>9030002</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1">
@@ -665,17 +728,43 @@
         <v>9030003</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="3" customFormat="1" ht="17.649999999999999">
+      <c r="A7" s="3">
+        <v>9030004</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="2" customFormat="1">
+      <c r="A8" s="2">
+        <v>9030005</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="3" customFormat="1"/>
-    <row r="8" spans="1:4" s="2" customFormat="1"/>
     <row r="9" spans="1:4" s="3" customFormat="1"/>
     <row r="10" spans="1:4" s="2" customFormat="1"/>
     <row r="11" spans="1:4" s="3" customFormat="1"/>
